--- a/sources/3E_Manha_2_Bimestre.xlsx
+++ b/sources/3E_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>245</x:t>
+    <x:t>320</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -222,240 +222,246 @@
     <x:t>17</x:t>
   </x:si>
   <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
     <x:t>16</x:t>
   </x:si>
   <x:si>
+    <x:t>58%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA BEATRIZ CAVALCANTI MATOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANNA LAURA DOS SANTOS ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOMINGOS VICTOR LUZOLO JOAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Não Comparecimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMANUELLY LORRAINE DE ASSIS DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELIPI GUSTAVO PAQUIELA DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERNANDO MEDEIROS DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL OLIVEIRA GONÇALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baixa - Transferência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL STEVANIN TAVARES JULIANO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GERTUDES ZAU MBUANGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAZIELLE BARROS DE MEDEIROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME ALVES VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME DOS SANTOS ARANTES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME SILVA DE PAULA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO CAETANO SOLOVIOW DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALANNA DE ALMEIDA OLTRAMARI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HENRY OLIVEIRA DE FRANÇA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IGOR CASTILHO PARAVANI DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSE XAVIER ALVES FILHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUAN DOS SANTOS MELO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETHICIA DOS SANTOS BORTUNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS EVANGELISTA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZ GUSTAVO MARIANO DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCUS VINICIUS DA COSTA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA EDUARDA RITA BATISTA VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIANA ESTEFANI FERREIRA MIRANDA</x:t>
+  </x:si>
+  <x:si>
     <x:t>60%</x:t>
   </x:si>
   <x:si>
-    <x:t>68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANA BEATRIZ CAVALCANTI MATOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANNA LAURA DOS SANTOS ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOMINGOS VICTOR LUZOLO JOAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Não Comparecimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMANUELLY LORRAINE DE ASSIS DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELIPI GUSTAVO PAQUIELA DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FERNANDO MEDEIROS DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL OLIVEIRA GONÇALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baixa - Transferência</x:t>
+    <x:t>MATHEUS ARTHUR FROTA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOISES BATISTA VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLE NOGUEIRA DAMIAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PABLO KILDEY DA SILVA RAMALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remanejamento</x:t>
   </x:si>
   <x:si>
     <x:t>76%</x:t>
   </x:si>
   <x:si>
-    <x:t>GABRIEL STEVANIN TAVARES JULIANO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GERTUDES ZAU MBUANGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAZIELLE BARROS DE MEDEIROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME ALVES VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME DOS SANTOS ARANTES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME SILVA DE PAULA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO CAETANO SOLOVIOW DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALANNA DE ALMEIDA OLTRAMARI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HENRY OLIVEIRA DE FRANÇA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IGOR CASTILHO PARAVANI DE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOSE XAVIER ALVES FILHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUAN DOS SANTOS MELO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETHICIA DOS SANTOS BORTUNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS EVANGELISTA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUIZ GUSTAVO MARIANO DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARCUS VINICIUS DA COSTA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA EDUARDA RITA BATISTA VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANA ESTEFANI FERREIRA MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72%</x:t>
+    <x:t>PAULO RICARDO PEREIRA LOPES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THAÍNA LEMES DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAQUEL POTENCIANA SANDA MPATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUAN ANDRADE DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>54%</x:t>
   </x:si>
   <x:si>
-    <x:t>MATHEUS ARTHUR FROTA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOISES BATISTA VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLE NOGUEIRA DAMIAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PABLO KILDEY DA SILVA RAMALHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanejamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULO RICARDO PEREIRA LOPES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THAÍNA LEMES DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAQUEL POTENCIANA SANDA MPATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUAN ANDRADE DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47%</x:t>
-  </x:si>
-  <x:si>
     <x:t>RYAN SOARES AQUINO</x:t>
   </x:si>
   <x:si>
@@ -465,42 +471,33 @@
     <x:t>VICTOR HIROSHI ASSAKAWA KASAMATU</x:t>
   </x:si>
   <x:si>
-    <x:t>81%</x:t>
+    <x:t>VINICIUS GIMENEZ DA COSTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WENDEL RAMOS DELFINO DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZION KALUEMBI SANTOS PORTELA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUMI EUGENIO URATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLAS MARCON MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANIELA RAMOS MIRANDA</x:t>
   </x:si>
   <x:si>
     <x:t>75%</x:t>
   </x:si>
   <x:si>
-    <x:t>VINICIUS GIMENEZ DA COSTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WENDEL RAMOS DELFINO DE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZION KALUEMBI SANTOS PORTELA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUMI EUGENIO URATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLAS MARCON MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DANIELA RAMOS MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74%</x:t>
-  </x:si>
-  <x:si>
     <x:t>ELOISE DE CARVALHO GONCALVES</x:t>
   </x:si>
   <x:si>
@@ -531,7 +528,13 @@
     <x:t>Aulas Dadas: 48</x:t>
   </x:si>
   <x:si>
+    <x:t>Aulas Dadas: 50</x:t>
+  </x:si>
+  <x:si>
     <x:t>Aulas Dadas: 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aulas Dadas: 25</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 10</x:t>
@@ -1572,13 +1575,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AJ13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM13" s="12">
         <x:v>1</x:v>
@@ -1596,13 +1599,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU13" s="12">
         <x:v>1</x:v>
@@ -1641,13 +1644,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG13" s="12">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BH13" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="BI13" s="12">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="BJ13" s="12" t="s">
         <x:v>57</x:v>
@@ -1760,13 +1763,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM14" s="12">
         <x:v>2</x:v>
@@ -1784,19 +1787,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
         <x:v>48</x:v>
@@ -1823,27 +1826,27 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BE14" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF14" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG14" s="12">
-        <x:v>99</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="BH14" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BI14" s="12">
-        <x:v>180</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="BJ14" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:62">
       <x:c r="A15" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>47</x:v>
@@ -1927,7 +1930,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
         <x:v>48</x:v>
@@ -1939,7 +1942,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG15" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH15" s="12" t="s">
         <x:v>49</x:v>
@@ -1948,13 +1951,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AJ15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM15" s="12">
         <x:v>3</x:v>
@@ -1972,13 +1975,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU15" s="12">
         <x:v>3</x:v>
@@ -1999,7 +2002,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA15" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>49</x:v>
@@ -2011,27 +2014,27 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BE15" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BF15" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG15" s="12">
-        <x:v>71</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BH15" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BI15" s="12">
-        <x:v>121</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="BJ15" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:62">
       <x:c r="A16" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>47</x:v>
@@ -2094,7 +2097,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="W16" s="12">
         <x:v>4</x:v>
@@ -2136,13 +2139,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AJ16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM16" s="12">
         <x:v>4</x:v>
@@ -2160,13 +2163,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU16" s="12">
         <x:v>4</x:v>
@@ -2199,30 +2202,30 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE16" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BF16" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG16" s="12">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BH16" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI16" s="12">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BJ16" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:62">
       <x:c r="A17" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="12">
         <x:v>5</x:v>
@@ -2327,10 +2330,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM17" s="12">
         <x:v>5</x:v>
@@ -2351,10 +2354,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU17" s="12">
         <x:v>5</x:v>
@@ -2396,21 +2399,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH17" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BI17" s="12">
         <x:v>171</x:v>
       </x:c>
       <x:c r="BJ17" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:62">
       <x:c r="A18" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
@@ -2503,7 +2506,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>49</x:v>
@@ -2515,10 +2518,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM18" s="12">
         <x:v>6</x:v>
@@ -2527,7 +2530,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
         <x:v>49</x:v>
@@ -2539,10 +2542,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU18" s="12">
         <x:v>6</x:v>
@@ -2575,7 +2578,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BE18" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BF18" s="12" t="s">
         <x:v>49</x:v>
@@ -2584,18 +2587,18 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="BH18" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BI18" s="12">
         <x:v>269</x:v>
       </x:c>
       <x:c r="BJ18" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:62">
       <x:c r="A19" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B19" s="12" t="s">
         <x:v>47</x:v>
@@ -2700,13 +2703,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AJ19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM19" s="12">
         <x:v>7</x:v>
@@ -2724,13 +2727,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU19" s="12">
         <x:v>7</x:v>
@@ -2769,21 +2772,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG19" s="12">
-        <x:v>49</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH19" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI19" s="12">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BJ19" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:62">
       <x:c r="A20" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
         <x:v>47</x:v>
@@ -2888,13 +2891,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM20" s="12">
         <x:v>8</x:v>
@@ -2912,13 +2915,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU20" s="12">
         <x:v>8</x:v>
@@ -2939,7 +2942,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BA20" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
         <x:v>49</x:v>
@@ -2957,24 +2960,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG20" s="12">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BH20" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI20" s="12">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BJ20" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:62">
       <x:c r="A21" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C21" s="12">
         <x:v>9</x:v>
@@ -3007,7 +3010,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>49</x:v>
@@ -3079,10 +3082,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM21" s="12">
         <x:v>9</x:v>
@@ -3103,10 +3106,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU21" s="12">
         <x:v>9</x:v>
@@ -3127,7 +3130,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BA21" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
         <x:v>49</x:v>
@@ -3148,13 +3151,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BH21" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BI21" s="12">
         <x:v>131</x:v>
       </x:c>
       <x:c r="BJ21" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:62">
@@ -3264,13 +3267,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM22" s="12">
         <x:v>10</x:v>
@@ -3288,13 +3291,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU22" s="12">
         <x:v>10</x:v>
@@ -3315,7 +3318,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA22" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB22" s="12" t="s">
         <x:v>49</x:v>
@@ -3333,21 +3336,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG22" s="12">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BH22" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI22" s="12">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BJ22" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:62">
       <x:c r="A23" s="11" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
         <x:v>47</x:v>
@@ -3383,7 +3386,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>49</x:v>
@@ -3452,13 +3455,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM23" s="12">
         <x:v>11</x:v>
@@ -3476,13 +3479,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU23" s="12">
         <x:v>11</x:v>
@@ -3503,7 +3506,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
         <x:v>49</x:v>
@@ -3521,16 +3524,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG23" s="12">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BH23" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BI23" s="12">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BJ23" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:62">
@@ -3571,7 +3574,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>49</x:v>
@@ -3640,13 +3643,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM24" s="12">
         <x:v>12</x:v>
@@ -3664,13 +3667,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU24" s="12">
         <x:v>12</x:v>
@@ -3709,16 +3712,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG24" s="12">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH24" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI24" s="12">
-        <x:v>68</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BJ24" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62">
@@ -3828,13 +3831,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AJ25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM25" s="12">
         <x:v>13</x:v>
@@ -3852,13 +3855,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU25" s="12">
         <x:v>13</x:v>
@@ -3897,21 +3900,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG25" s="12">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BH25" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI25" s="12">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BJ25" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:62">
       <x:c r="A26" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B26" s="12" t="s">
         <x:v>47</x:v>
@@ -3947,7 +3950,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
         <x:v>49</x:v>
@@ -4016,13 +4019,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM26" s="12">
         <x:v>14</x:v>
@@ -4040,13 +4043,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU26" s="12">
         <x:v>14</x:v>
@@ -4085,21 +4088,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG26" s="12">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BH26" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BI26" s="12">
-        <x:v>121</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="BJ26" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:62">
       <x:c r="A27" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
         <x:v>47</x:v>
@@ -4183,7 +4186,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>61</x:v>
@@ -4195,7 +4198,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>49</x:v>
@@ -4204,13 +4207,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM27" s="12">
         <x:v>15</x:v>
@@ -4228,13 +4231,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU27" s="12">
         <x:v>15</x:v>
@@ -4255,7 +4258,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
         <x:v>49</x:v>
@@ -4273,21 +4276,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG27" s="12">
-        <x:v>60</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BH27" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI27" s="12">
-        <x:v>114</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BJ27" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:62">
       <x:c r="A28" s="11" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>47</x:v>
@@ -4392,13 +4395,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM28" s="12">
         <x:v>16</x:v>
@@ -4416,13 +4419,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU28" s="12">
         <x:v>16</x:v>
@@ -4443,7 +4446,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
         <x:v>49</x:v>
@@ -4461,21 +4464,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG28" s="12">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BH28" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BI28" s="12">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BJ28" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
       <x:c r="A29" s="11" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>47</x:v>
@@ -4580,13 +4583,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM29" s="12">
         <x:v>17</x:v>
@@ -4604,13 +4607,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU29" s="12">
         <x:v>17</x:v>
@@ -4649,21 +4652,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>101</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
       <x:c r="A30" s="11" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>47</x:v>
@@ -4699,7 +4702,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>49</x:v>
@@ -4768,13 +4771,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM30" s="12">
         <x:v>18</x:v>
@@ -4792,13 +4795,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU30" s="12">
         <x:v>18</x:v>
@@ -4837,21 +4840,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>47</x:v>
@@ -4887,7 +4890,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4956,13 +4959,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM31" s="12">
         <x:v>19</x:v>
@@ -4980,13 +4983,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU31" s="12">
         <x:v>19</x:v>
@@ -5025,21 +5028,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>47</x:v>
@@ -5075,7 +5078,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>49</x:v>
@@ -5144,13 +5147,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM32" s="12">
         <x:v>20</x:v>
@@ -5168,19 +5171,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
         <x:v>54</x:v>
@@ -5213,21 +5216,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
       <x:c r="A33" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>47</x:v>
@@ -5263,10 +5266,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O33" s="12">
         <x:v>21</x:v>
@@ -5332,13 +5335,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM33" s="12">
         <x:v>21</x:v>
@@ -5356,13 +5359,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU33" s="12">
         <x:v>21</x:v>
@@ -5383,10 +5386,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BC33" s="12">
         <x:v>21</x:v>
@@ -5401,21 +5404,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI33" s="12">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:62">
       <x:c r="A34" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>47</x:v>
@@ -5520,13 +5523,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM34" s="12">
         <x:v>22</x:v>
@@ -5544,13 +5547,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU34" s="12">
         <x:v>22</x:v>
@@ -5589,21 +5592,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="BI34" s="12">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="BI34" s="12">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
       <x:c r="A35" s="11" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>47</x:v>
@@ -5708,13 +5711,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM35" s="12">
         <x:v>23</x:v>
@@ -5732,13 +5735,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU35" s="12">
         <x:v>23</x:v>
@@ -5777,21 +5780,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG35" s="12">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH35" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BI35" s="12">
-        <x:v>60</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
       <x:c r="A36" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>47</x:v>
@@ -5872,10 +5875,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>48</x:v>
@@ -5896,13 +5899,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM36" s="12">
         <x:v>24</x:v>
@@ -5920,13 +5923,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU36" s="12">
         <x:v>24</x:v>
@@ -5965,21 +5968,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG36" s="12">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BH36" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="BI36" s="12">
-        <x:v>177</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="BJ36" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
       <x:c r="A37" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
         <x:v>47</x:v>
@@ -6084,13 +6087,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM37" s="12">
         <x:v>25</x:v>
@@ -6108,13 +6111,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU37" s="12">
         <x:v>25</x:v>
@@ -6153,24 +6156,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI37" s="12">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
       <x:c r="A38" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
@@ -6191,7 +6194,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -6248,10 +6251,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
         <x:v>49</x:v>
@@ -6263,7 +6266,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6275,10 +6278,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM38" s="12">
         <x:v>26</x:v>
@@ -6287,7 +6290,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
         <x:v>49</x:v>
@@ -6299,10 +6302,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU38" s="12">
         <x:v>26</x:v>
@@ -6335,7 +6338,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BE38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF38" s="12" t="s">
         <x:v>49</x:v>
@@ -6344,18 +6347,18 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BI38" s="12">
         <x:v>298</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>47</x:v>
@@ -6391,7 +6394,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>49</x:v>
@@ -6460,13 +6463,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM39" s="12">
         <x:v>27</x:v>
@@ -6484,13 +6487,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU39" s="12">
         <x:v>27</x:v>
@@ -6511,7 +6514,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
@@ -6529,24 +6532,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>94</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C40" s="12">
         <x:v>28</x:v>
@@ -6651,10 +6654,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM40" s="12">
         <x:v>28</x:v>
@@ -6675,10 +6678,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU40" s="12">
         <x:v>28</x:v>
@@ -6720,18 +6723,18 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>127</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI40" s="12">
         <x:v>247</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62">
       <x:c r="A41" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>47</x:v>
@@ -6794,7 +6797,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
@@ -6836,13 +6839,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AJ41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM41" s="12">
         <x:v>29</x:v>
@@ -6860,13 +6863,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU41" s="12">
         <x:v>29</x:v>
@@ -6905,21 +6908,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="BI41" s="12">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="BI41" s="12">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
         <x:v>47</x:v>
@@ -7015,7 +7018,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>49</x:v>
@@ -7024,13 +7027,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM42" s="12">
         <x:v>30</x:v>
@@ -7048,13 +7051,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU42" s="12">
         <x:v>30</x:v>
@@ -7093,21 +7096,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>90</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
       <x:c r="A43" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
         <x:v>47</x:v>
@@ -7212,13 +7215,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM43" s="12">
         <x:v>31</x:v>
@@ -7236,13 +7239,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU43" s="12">
         <x:v>31</x:v>
@@ -7281,24 +7284,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
       <x:c r="A44" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
@@ -7403,10 +7406,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM44" s="12">
         <x:v>32</x:v>
@@ -7427,10 +7430,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU44" s="12">
         <x:v>32</x:v>
@@ -7472,18 +7475,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="BI44" s="12">
         <x:v>148</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
       <x:c r="A45" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>47</x:v>
@@ -7588,13 +7591,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM45" s="12">
         <x:v>33</x:v>
@@ -7612,13 +7615,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU45" s="12">
         <x:v>33</x:v>
@@ -7657,21 +7660,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:62">
       <x:c r="A46" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>47</x:v>
@@ -7707,7 +7710,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>49</x:v>
@@ -7734,7 +7737,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="W46" s="12">
         <x:v>34</x:v>
@@ -7776,13 +7779,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM46" s="12">
         <x:v>34</x:v>
@@ -7800,13 +7803,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU46" s="12">
         <x:v>34</x:v>
@@ -7827,7 +7830,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
         <x:v>49</x:v>
@@ -7845,21 +7848,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BI46" s="12">
-        <x:v>127</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>98</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>47</x:v>
@@ -7964,13 +7967,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM47" s="12">
         <x:v>35</x:v>
@@ -7988,13 +7991,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU47" s="12">
         <x:v>35</x:v>
@@ -8033,24 +8036,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
@@ -8080,7 +8083,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
         <x:v>55</x:v>
@@ -8128,7 +8131,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
         <x:v>62</x:v>
@@ -8143,7 +8146,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -8155,10 +8158,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM48" s="12">
         <x:v>36</x:v>
@@ -8167,7 +8170,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
         <x:v>49</x:v>
@@ -8179,10 +8182,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU48" s="12">
         <x:v>36</x:v>
@@ -8215,7 +8218,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
         <x:v>49</x:v>
@@ -8224,18 +8227,18 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>140</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BI48" s="12">
         <x:v>285</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>47</x:v>
@@ -8316,7 +8319,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
         <x:v>55</x:v>
@@ -8340,13 +8343,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM49" s="12">
         <x:v>37</x:v>
@@ -8364,19 +8367,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
         <x:v>51</x:v>
@@ -8409,21 +8412,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>99</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
         <x:v>47</x:v>
@@ -8459,7 +8462,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>49</x:v>
@@ -8486,7 +8489,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="W50" s="12">
         <x:v>38</x:v>
@@ -8528,13 +8531,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM50" s="12">
         <x:v>38</x:v>
@@ -8552,13 +8555,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU50" s="12">
         <x:v>38</x:v>
@@ -8597,24 +8600,24 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>45</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="BI50" s="12">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
@@ -8719,10 +8722,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM51" s="12">
         <x:v>39</x:v>
@@ -8743,10 +8746,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU51" s="12">
         <x:v>39</x:v>
@@ -8788,13 +8791,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI51" s="12">
         <x:v>133</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
@@ -8802,7 +8805,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
@@ -8907,10 +8910,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM52" s="12">
         <x:v>40</x:v>
@@ -8931,10 +8934,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU52" s="12">
         <x:v>40</x:v>
@@ -8976,13 +8979,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH52" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BI52" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
@@ -9050,7 +9053,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="W53" s="12">
         <x:v>41</x:v>
@@ -9083,7 +9086,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -9092,13 +9095,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM53" s="12">
         <x:v>41</x:v>
@@ -9116,13 +9119,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU53" s="12">
         <x:v>41</x:v>
@@ -9161,21 +9164,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>114</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
       <x:c r="A54" s="11" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B54" s="12" t="s">
         <x:v>47</x:v>
@@ -9280,13 +9283,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM54" s="12">
         <x:v>42</x:v>
@@ -9304,13 +9307,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU54" s="12">
         <x:v>42</x:v>
@@ -9349,21 +9352,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
       <x:c r="A55" s="11" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B55" s="12" t="s">
         <x:v>47</x:v>
@@ -9399,7 +9402,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
         <x:v>59</x:v>
@@ -9468,13 +9471,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM55" s="12">
         <x:v>43</x:v>
@@ -9492,19 +9495,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
         <x:v>49</x:v>
@@ -9537,21 +9540,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
       <x:c r="A56" s="11" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
         <x:v>47</x:v>
@@ -9656,13 +9659,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM56" s="12">
         <x:v>44</x:v>
@@ -9680,13 +9683,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU56" s="12">
         <x:v>44</x:v>
@@ -9725,21 +9728,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>77</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
       <x:c r="A57" s="11" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
         <x:v>47</x:v>
@@ -9844,13 +9847,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM57" s="12">
         <x:v>45</x:v>
@@ -9868,13 +9871,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU57" s="12">
         <x:v>45</x:v>
@@ -9895,7 +9898,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
         <x:v>49</x:v>
@@ -9913,13 +9916,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
         <x:v>57</x:v>
@@ -9927,7 +9930,7 @@
     </x:row>
     <x:row r="58" spans="1:62">
       <x:c r="A58" s="11" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
         <x:v>47</x:v>
@@ -9948,7 +9951,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
         <x:v>48</x:v>
@@ -10023,7 +10026,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>49</x:v>
@@ -10032,13 +10035,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AL58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM58" s="12">
         <x:v>46</x:v>
@@ -10056,13 +10059,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU58" s="12">
         <x:v>46</x:v>
@@ -10083,7 +10086,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
         <x:v>49</x:v>
@@ -10101,21 +10104,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG58" s="12">
-        <x:v>63</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="BI58" s="12">
-        <x:v>63</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
         <x:v>47</x:v>
@@ -10220,13 +10223,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM59" s="12">
         <x:v>47</x:v>
@@ -10244,13 +10247,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU59" s="12">
         <x:v>47</x:v>
@@ -10271,7 +10274,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
         <x:v>49</x:v>
@@ -10289,21 +10292,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>65</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>65</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>47</x:v>
@@ -10339,7 +10342,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="M60" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N60" s="12" t="s">
         <x:v>49</x:v>
@@ -10408,13 +10411,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM60" s="12">
         <x:v>48</x:v>
@@ -10432,13 +10435,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AR60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU60" s="12">
         <x:v>48</x:v>
@@ -10459,7 +10462,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="BA60" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
         <x:v>49</x:v>
@@ -10477,21 +10480,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
       <x:c r="A61" s="11" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>47</x:v>
@@ -10599,10 +10602,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM61" s="12">
         <x:v>49</x:v>
@@ -10623,16 +10626,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
         <x:v>49</x:v>
@@ -10644,7 +10647,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
         <x:v>49</x:v>
@@ -10656,7 +10659,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
         <x:v>54</x:v>
@@ -10668,18 +10671,18 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="BI61" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
       <x:c r="A62" s="11" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
         <x:v>47</x:v>
@@ -10787,10 +10790,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM62" s="12">
         <x:v>50</x:v>
@@ -10811,16 +10814,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
         <x:v>49</x:v>
@@ -10856,72 +10859,72 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BI62" s="12">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
       <x:c r="A63" s="13" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B63" s="13" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C63" s="7" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="B63" s="13" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C63" s="7" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="D63" s="7"/>
       <x:c r="E63" s="7"/>
       <x:c r="F63" s="7"/>
       <x:c r="G63" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H63" s="7"/>
       <x:c r="I63" s="7"/>
       <x:c r="J63" s="7"/>
       <x:c r="K63" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="L63" s="7"/>
       <x:c r="M63" s="7"/>
       <x:c r="N63" s="7"/>
       <x:c r="O63" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="P63" s="7"/>
       <x:c r="Q63" s="7"/>
       <x:c r="R63" s="7"/>
       <x:c r="S63" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="T63" s="7"/>
       <x:c r="U63" s="7"/>
       <x:c r="V63" s="7"/>
       <x:c r="W63" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="X63" s="7"/>
       <x:c r="Y63" s="7"/>
       <x:c r="Z63" s="7"/>
       <x:c r="AA63" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="AB63" s="7"/>
       <x:c r="AC63" s="7"/>
       <x:c r="AD63" s="7"/>
       <x:c r="AE63" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="AF63" s="7"/>
       <x:c r="AG63" s="7"/>
       <x:c r="AH63" s="7"/>
       <x:c r="AI63" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="AJ63" s="7"/>
       <x:c r="AK63" s="7"/>
@@ -10933,25 +10936,25 @@
       <x:c r="AO63" s="7"/>
       <x:c r="AP63" s="7"/>
       <x:c r="AQ63" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AR63" s="7"/>
       <x:c r="AS63" s="7"/>
       <x:c r="AT63" s="7"/>
       <x:c r="AU63" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="AV63" s="7"/>
       <x:c r="AW63" s="7"/>
       <x:c r="AX63" s="7"/>
       <x:c r="AY63" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AZ63" s="7"/>
       <x:c r="BA63" s="7"/>
       <x:c r="BB63" s="7"/>
       <x:c r="BC63" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="BD63" s="7"/>
       <x:c r="BE63" s="7"/>
@@ -10963,37 +10966,37 @@
     </x:row>
     <x:row r="65" spans="1:62">
       <x:c r="A65" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:62">
       <x:c r="A66" s="13" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:62">
       <x:c r="A67" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:62">
       <x:c r="A68" s="13" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:62">
       <x:c r="A69" s="13" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:62">
       <x:c r="A70" s="13" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:62">
       <x:c r="A71" s="13" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/sources/3E_Manha_2_Bimestre.xlsx
+++ b/sources/3E_Manha_2_Bimestre.xlsx
@@ -207,45 +207,48 @@
     <x:t>ALLAN FELIPE DE OLIVEIRA ALVES</x:t>
   </x:si>
   <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA BEATRIZ CAVALCANTI MATOS</x:t>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>67%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANA BEATRIZ CAVALCANTI MATOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
     <x:t>72%</x:t>
   </x:si>
   <x:si>
@@ -261,6 +264,12 @@
     <x:t>84%</x:t>
   </x:si>
   <x:si>
+    <x:t>DANIELA RAMOS MIRANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75%</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOMINGOS VICTOR LUZOLO JOAO</x:t>
   </x:si>
   <x:si>
@@ -270,6 +279,12 @@
     <x:t>100%</x:t>
   </x:si>
   <x:si>
+    <x:t>73%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELOISE DE CARVALHO GONCALVES</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMANUELLY LORRAINE DE ASSIS DE OLIVEIRA</x:t>
   </x:si>
   <x:si>
@@ -279,187 +294,193 @@
     <x:t>65%</x:t>
   </x:si>
   <x:si>
+    <x:t>FELIPI GUSTAVO PAQUIELA DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERNANDO MEDEIROS DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL OLIVEIRA GONÇALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baixa - Transferência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIEL STEVANIN TAVARES JULIANO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GERTUDES ZAU MBUANGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAZIELLE BARROS DE MEDEIROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME ALVES VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME DOS SANTOS ARANTES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUILHERME SILVA DE PAULA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO CAETANO SOLOVIOW DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALANNA DE ALMEIDA OLTRAMARI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HENRY OLIVEIRA DE FRANÇA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IGOR CASTILHO PARAVANI DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSE XAVIER ALVES FILHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAUAN DOS SANTOS MELO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETHICIA DOS SANTOS BORTUNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS EVANGELISTA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZ GUSTAVO MARIANO DO NASCIMENTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCUS VINICIUS DA COSTA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIA EDUARDA RITA BATISTA VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIANA ESTEFANI FERREIRA MIRANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARIANE DUARTE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transferido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS ARTHUR FROTA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MATHEUS DOS SANTOS GENIAL LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOISES BATISTA VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLAS MARCON MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NICOLE NOGUEIRA DAMIAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PABLO KILDEY DA SILVA RAMALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Remanejamento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULO RICARDO PEREIRA LOPES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THAÍNA LEMES DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAQUEL POTENCIANA SANDA MPATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUAN ANDRADE DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
     <x:t>56%</x:t>
   </x:si>
   <x:si>
-    <x:t>FELIPI GUSTAVO PAQUIELA DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FERNANDO MEDEIROS DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL OLIVEIRA GONÇALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baixa - Transferência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIEL STEVANIN TAVARES JULIANO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GERTUDES ZAU MBUANGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAZIELLE BARROS DE MEDEIROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME ALVES VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME DOS SANTOS ARANTES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUILHERME SILVA DE PAULA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUSTAVO CAETANO SOLOVIOW DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALANNA DE ALMEIDA OLTRAMARI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HENRY OLIVEIRA DE FRANÇA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IGOR CASTILHO PARAVANI DE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA ARCHAPA NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOSE XAVIER ALVES FILHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUAN DOS SANTOS MELO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETHICIA DOS SANTOS BORTUNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS EVANGELISTA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUIZ GUSTAVO MARIANO DO NASCIMENTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARCUS VINICIUS DA COSTA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIA EDUARDA RITA BATISTA VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANA ESTEFANI FERREIRA MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS ARTHUR FROTA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOISES BATISTA VIEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLE NOGUEIRA DAMIAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PABLO KILDEY DA SILVA RAMALHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanejamento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULO RICARDO PEREIRA LOPES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THAÍNA LEMES DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAQUEL POTENCIANA SANDA MPATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUAN ANDRADE DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54%</x:t>
+    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
   </x:si>
   <x:si>
     <x:t>RYAN SOARES AQUINO</x:t>
@@ -471,6 +492,9 @@
     <x:t>VICTOR HIROSHI ASSAKAWA KASAMATU</x:t>
   </x:si>
   <x:si>
+    <x:t>VINICIUS ALVES ROCHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>VINICIUS GIMENEZ DA COSTA</x:t>
   </x:si>
   <x:si>
@@ -480,34 +504,10 @@
     <x:t>63%</x:t>
   </x:si>
   <x:si>
+    <x:t>YUMI EUGENIO URATA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZION KALUEMBI SANTOS PORTELA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUMI EUGENIO URATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYAN GUEDES DE BRITO FRANCISCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NICOLAS MARCON MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DANIELA RAMOS MIRANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELOISE DE CARVALHO GONCALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MATHEUS DOS SANTOS GENIAL LIMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VINICIUS ALVES ROCHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARIANE DUARTE SOUZA</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -1611,7 +1611,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AV13" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW13" s="12" t="s">
         <x:v>51</x:v>
@@ -1679,10 +1679,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="I14" s="12" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
         <x:v>49</x:v>
@@ -1691,13 +1691,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M14" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N14" s="12" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="M14" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N14" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="O14" s="12">
         <x:v>2</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
         <x:v>51</x:v>
@@ -1733,7 +1733,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA14" s="12">
         <x:v>2</x:v>
@@ -1742,10 +1742,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD14" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AE14" s="12">
         <x:v>2</x:v>
@@ -1769,7 +1769,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="AL14" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AM14" s="12">
         <x:v>2</x:v>
@@ -1778,7 +1778,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP14" s="12" t="s">
         <x:v>49</x:v>
@@ -1790,7 +1790,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
         <x:v>49</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW14" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AY14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AZ14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA14" s="12" t="s">
         <x:v>51</x:v>
@@ -1838,7 +1838,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="BI14" s="12">
-        <x:v>214</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="BJ14" s="12" t="s">
         <x:v>68</x:v>
@@ -1870,10 +1870,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I15" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J15" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K15" s="12">
         <x:v>3</x:v>
@@ -1930,7 +1930,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD15" s="12" t="s">
         <x:v>48</x:v>
@@ -2002,7 +2002,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BA15" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB15" s="12" t="s">
         <x:v>49</x:v>
@@ -2011,7 +2011,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BD15" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE15" s="12" t="s">
         <x:v>71</x:v>
@@ -2023,18 +2023,18 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="BH15" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI15" s="12">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BJ15" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:62">
       <x:c r="A16" s="11" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>47</x:v>
@@ -2058,7 +2058,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J16" s="12" t="s">
         <x:v>49</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
         <x:v>66</x:v>
@@ -2103,7 +2103,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
         <x:v>51</x:v>
@@ -2121,7 +2121,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AD16" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AE16" s="12">
         <x:v>4</x:v>
@@ -2211,30 +2211,30 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="BH16" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI16" s="12">
         <x:v>101</x:v>
       </x:c>
       <x:c r="BJ16" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:62">
       <x:c r="A17" s="11" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
         <x:v>49</x:v>
@@ -2243,10 +2243,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J17" s="12" t="s">
         <x:v>49</x:v>
@@ -2255,10 +2255,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N17" s="12" t="s">
         <x:v>49</x:v>
@@ -2279,10 +2279,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="T17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
         <x:v>49</x:v>
@@ -2291,10 +2291,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="X17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
         <x:v>49</x:v>
@@ -2303,10 +2303,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AB17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD17" s="12" t="s">
         <x:v>49</x:v>
@@ -2315,10 +2315,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH17" s="12" t="s">
         <x:v>49</x:v>
@@ -2327,10 +2327,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AJ17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AL17" s="12" t="s">
         <x:v>49</x:v>
@@ -2339,10 +2339,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP17" s="12" t="s">
         <x:v>49</x:v>
@@ -2351,10 +2351,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AR17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT17" s="12" t="s">
         <x:v>49</x:v>
@@ -2363,22 +2363,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AZ17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB17" s="12" t="s">
         <x:v>49</x:v>
@@ -2387,25 +2387,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="BD17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE17" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF17" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG17" s="12">
-        <x:v>0</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BH17" s="12" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="BI17" s="12">
-        <x:v>171</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BJ17" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:62">
@@ -2413,7 +2413,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B18" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
@@ -2422,7 +2422,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F18" s="12" t="s">
         <x:v>49</x:v>
@@ -2434,7 +2434,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J18" s="12" t="s">
         <x:v>49</x:v>
@@ -2446,7 +2446,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N18" s="12" t="s">
         <x:v>49</x:v>
@@ -2470,7 +2470,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V18" s="12" t="s">
         <x:v>49</x:v>
@@ -2482,7 +2482,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
         <x:v>49</x:v>
@@ -2494,7 +2494,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD18" s="12" t="s">
         <x:v>49</x:v>
@@ -2506,7 +2506,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH18" s="12" t="s">
         <x:v>49</x:v>
@@ -2530,7 +2530,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP18" s="12" t="s">
         <x:v>49</x:v>
@@ -2554,10 +2554,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AW18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY18" s="12">
         <x:v>6</x:v>
@@ -2566,7 +2566,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="BA18" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB18" s="12" t="s">
         <x:v>49</x:v>
@@ -2575,22 +2575,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="BD18" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE18" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF18" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG18" s="12">
-        <x:v>111</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH18" s="12" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="BI18" s="12">
-        <x:v>269</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="BJ18" s="12" t="s">
         <x:v>83</x:v>
@@ -2607,10 +2607,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
         <x:v>49</x:v>
@@ -2619,10 +2619,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I19" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J19" s="12" t="s">
         <x:v>49</x:v>
@@ -2655,22 +2655,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="T19" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U19" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="V19" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W19" s="12">
         <x:v>7</x:v>
       </x:c>
       <x:c r="X19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z19" s="12" t="s">
         <x:v>49</x:v>
@@ -2679,10 +2679,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="s">
         <x:v>49</x:v>
@@ -2691,10 +2691,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AF19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH19" s="12" t="s">
         <x:v>49</x:v>
@@ -2706,7 +2706,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK19" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL19" s="12" t="s">
         <x:v>49</x:v>
@@ -2727,7 +2727,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
         <x:v>51</x:v>
@@ -2739,10 +2739,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW19" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
         <x:v>49</x:v>
@@ -2751,10 +2751,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AZ19" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA19" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB19" s="12" t="s">
         <x:v>49</x:v>
@@ -2763,7 +2763,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="BD19" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE19" s="12" t="s">
         <x:v>50</x:v>
@@ -2772,33 +2772,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG19" s="12">
-        <x:v>67</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BH19" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BI19" s="12">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="BJ19" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:62">
       <x:c r="A20" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B20" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D20" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="12" t="s">
         <x:v>49</x:v>
@@ -2807,10 +2807,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J20" s="12" t="s">
         <x:v>49</x:v>
@@ -2819,10 +2819,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>49</x:v>
@@ -2843,22 +2843,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
         <x:v>49</x:v>
@@ -2867,10 +2867,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD20" s="12" t="s">
         <x:v>49</x:v>
@@ -2879,10 +2879,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AF20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
         <x:v>49</x:v>
@@ -2891,10 +2891,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AJ20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL20" s="12" t="s">
         <x:v>49</x:v>
@@ -2903,10 +2903,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AP20" s="12" t="s">
         <x:v>49</x:v>
@@ -2915,10 +2915,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
         <x:v>49</x:v>
@@ -2927,10 +2927,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW20" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
         <x:v>49</x:v>
@@ -2939,10 +2939,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AZ20" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA20" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB20" s="12" t="s">
         <x:v>49</x:v>
@@ -2951,39 +2951,39 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="BD20" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE20" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BF20" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG20" s="12">
-        <x:v>36</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="BH20" s="12" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="BI20" s="12">
-        <x:v>85</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="BJ20" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:62">
       <x:c r="A21" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="12" t="s">
         <x:v>54</x:v>
@@ -2995,10 +2995,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
         <x:v>49</x:v>
@@ -3007,10 +3007,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>49</x:v>
@@ -3031,22 +3031,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="T21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="W21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
         <x:v>49</x:v>
@@ -3055,10 +3055,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>49</x:v>
@@ -3067,10 +3067,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>49</x:v>
@@ -3079,10 +3079,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AJ21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>49</x:v>
@@ -3091,10 +3091,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP21" s="12" t="s">
         <x:v>49</x:v>
@@ -3103,10 +3103,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
         <x:v>49</x:v>
@@ -3115,22 +3115,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AV21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY21" s="12">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AZ21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BA21" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB21" s="12" t="s">
         <x:v>49</x:v>
@@ -3139,30 +3139,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="BD21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE21" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF21" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG21" s="12">
-        <x:v>19</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH21" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI21" s="12">
-        <x:v>131</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BJ21" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:62">
       <x:c r="A22" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>47</x:v>
@@ -3171,7 +3171,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="12" t="s">
         <x:v>49</x:v>
@@ -3183,10 +3183,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I22" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J22" s="12" t="s">
         <x:v>49</x:v>
@@ -3195,7 +3195,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M22" s="12" t="s">
         <x:v>54</x:v>
@@ -3219,13 +3219,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W22" s="12">
         <x:v>10</x:v>
@@ -3234,7 +3234,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
         <x:v>49</x:v>
@@ -3243,10 +3243,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AB22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>49</x:v>
@@ -3258,7 +3258,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH22" s="12" t="s">
         <x:v>49</x:v>
@@ -3267,10 +3267,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AJ22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK22" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL22" s="12" t="s">
         <x:v>49</x:v>
@@ -3282,7 +3282,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP22" s="12" t="s">
         <x:v>49</x:v>
@@ -3291,10 +3291,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
         <x:v>49</x:v>
@@ -3303,7 +3303,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW22" s="12" t="s">
         <x:v>54</x:v>
@@ -3315,10 +3315,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AZ22" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA22" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB22" s="12" t="s">
         <x:v>49</x:v>
@@ -3327,39 +3327,39 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="BD22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE22" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF22" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG22" s="12">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="BH22" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI22" s="12">
-        <x:v>73</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BJ22" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:62">
       <x:c r="A23" s="11" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B23" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E23" s="12" t="s">
         <x:v>54</x:v>
@@ -3371,7 +3371,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I23" s="12" t="s">
         <x:v>49</x:v>
@@ -3383,10 +3383,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N23" s="12" t="s">
         <x:v>49</x:v>
@@ -3407,22 +3407,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="V23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
         <x:v>49</x:v>
@@ -3431,22 +3431,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AB23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AD23" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE23" s="12">
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH23" s="12" t="s">
         <x:v>49</x:v>
@@ -3455,10 +3455,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL23" s="12" t="s">
         <x:v>49</x:v>
@@ -3467,7 +3467,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
         <x:v>54</x:v>
@@ -3479,7 +3479,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
         <x:v>49</x:v>
@@ -3491,7 +3491,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW23" s="12" t="s">
         <x:v>49</x:v>
@@ -3503,10 +3503,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AZ23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB23" s="12" t="s">
         <x:v>49</x:v>
@@ -3515,7 +3515,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="BD23" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE23" s="12" t="s">
         <x:v>51</x:v>
@@ -3524,21 +3524,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG23" s="12">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BH23" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BI23" s="12">
-        <x:v>77</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="BJ23" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:62">
       <x:c r="A24" s="11" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B24" s="12" t="s">
         <x:v>47</x:v>
@@ -3547,10 +3547,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>49</x:v>
@@ -3559,10 +3559,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I24" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J24" s="12" t="s">
         <x:v>49</x:v>
@@ -3571,10 +3571,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N24" s="12" t="s">
         <x:v>49</x:v>
@@ -3595,22 +3595,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W24" s="12">
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z24" s="12" t="s">
         <x:v>49</x:v>
@@ -3619,10 +3619,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AB24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD24" s="12" t="s">
         <x:v>49</x:v>
@@ -3631,10 +3631,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AF24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>49</x:v>
@@ -3643,10 +3643,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AK24" s="12" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="AK24" s="12" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="AL24" s="12" t="s">
         <x:v>49</x:v>
@@ -3655,10 +3655,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AN24" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>49</x:v>
@@ -3667,10 +3667,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
         <x:v>49</x:v>
@@ -3691,10 +3691,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AZ24" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA24" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB24" s="12" t="s">
         <x:v>49</x:v>
@@ -3706,22 +3706,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BE24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF24" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG24" s="12">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BH24" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BI24" s="12">
-        <x:v>85</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BJ24" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62">
@@ -3735,10 +3735,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F25" s="12" t="s">
         <x:v>49</x:v>
@@ -3762,7 +3762,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N25" s="12" t="s">
         <x:v>49</x:v>
@@ -3783,7 +3783,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U25" s="12" t="s">
         <x:v>51</x:v>
@@ -3795,7 +3795,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
         <x:v>50</x:v>
@@ -3807,13 +3807,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AD25" s="12" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="AD25" s="12" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="AE25" s="12">
         <x:v>13</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK25" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL25" s="12" t="s">
         <x:v>49</x:v>
@@ -3846,7 +3846,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP25" s="12" t="s">
         <x:v>49</x:v>
@@ -3882,7 +3882,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB25" s="12" t="s">
         <x:v>49</x:v>
@@ -3891,25 +3891,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="BD25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE25" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF25" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG25" s="12">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="BH25" s="12" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="BI25" s="12">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BJ25" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:62">
@@ -3923,10 +3923,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
         <x:v>49</x:v>
@@ -3935,10 +3935,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="H26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
         <x:v>49</x:v>
@@ -3947,10 +3947,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M26" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N26" s="12" t="s">
         <x:v>49</x:v>
@@ -3971,13 +3971,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="T26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="W26" s="12">
         <x:v>14</x:v>
@@ -3986,7 +3986,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
         <x:v>49</x:v>
@@ -3995,22 +3995,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE26" s="12">
         <x:v>14</x:v>
       </x:c>
       <x:c r="AF26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AH26" s="12" t="s">
         <x:v>49</x:v>
@@ -4019,10 +4019,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AJ26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK26" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AL26" s="12" t="s">
         <x:v>49</x:v>
@@ -4034,7 +4034,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AO26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP26" s="12" t="s">
         <x:v>49</x:v>
@@ -4043,7 +4043,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
         <x:v>54</x:v>
@@ -4055,10 +4055,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AW26" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
         <x:v>49</x:v>
@@ -4067,10 +4067,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AZ26" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB26" s="12" t="s">
         <x:v>49</x:v>
@@ -4079,25 +4079,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="BD26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE26" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF26" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG26" s="12">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH26" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI26" s="12">
-        <x:v>137</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BJ26" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:62">
@@ -4111,10 +4111,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
         <x:v>49</x:v>
@@ -4123,10 +4123,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
         <x:v>49</x:v>
@@ -4135,10 +4135,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N27" s="12" t="s">
         <x:v>49</x:v>
@@ -4159,22 +4159,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
         <x:v>49</x:v>
@@ -4183,22 +4183,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AE27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
         <x:v>49</x:v>
@@ -4207,10 +4207,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
         <x:v>49</x:v>
@@ -4219,10 +4219,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
         <x:v>49</x:v>
@@ -4231,10 +4231,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
         <x:v>49</x:v>
@@ -4243,10 +4243,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
         <x:v>49</x:v>
@@ -4255,10 +4255,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
         <x:v>49</x:v>
@@ -4267,25 +4267,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="BD27" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE27" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF27" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG27" s="12">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BH27" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI27" s="12">
-        <x:v>126</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BJ27" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:62">
@@ -4299,10 +4299,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
         <x:v>49</x:v>
@@ -4311,22 +4311,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="L28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N28" s="12" t="s">
         <x:v>49</x:v>
@@ -4347,13 +4347,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W28" s="12">
         <x:v>16</x:v>
@@ -4362,7 +4362,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
         <x:v>49</x:v>
@@ -4371,22 +4371,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AE28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>49</x:v>
@@ -4398,7 +4398,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
         <x:v>49</x:v>
@@ -4407,10 +4407,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
         <x:v>49</x:v>
@@ -4431,7 +4431,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
         <x:v>50</x:v>
@@ -4443,10 +4443,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
         <x:v>49</x:v>
@@ -4455,25 +4455,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="BD28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF28" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG28" s="12">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BH28" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="BI28" s="12">
-        <x:v>99</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="BJ28" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:62">
@@ -4490,7 +4490,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>49</x:v>
@@ -4499,10 +4499,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
         <x:v>49</x:v>
@@ -4511,7 +4511,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="L29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M29" s="12" t="s">
         <x:v>54</x:v>
@@ -4535,46 +4535,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AC29" s="12" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="AD29" s="12" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="AC29" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AD29" s="12" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="AE29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>49</x:v>
@@ -4586,7 +4586,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>49</x:v>
@@ -4595,10 +4595,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>49</x:v>
@@ -4607,7 +4607,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
         <x:v>51</x:v>
@@ -4619,10 +4619,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>49</x:v>
@@ -4631,10 +4631,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
         <x:v>49</x:v>
@@ -4643,30 +4643,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE29" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG29" s="12">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BH29" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BI29" s="12">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="BJ29" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:62">
       <x:c r="A30" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>47</x:v>
@@ -4678,7 +4678,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>49</x:v>
@@ -4687,22 +4687,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="L30" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M30" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N30" s="12" t="s">
         <x:v>49</x:v>
@@ -4723,19 +4723,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
         <x:v>54</x:v>
@@ -4747,10 +4747,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>49</x:v>
@@ -4759,10 +4759,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH30" s="12" t="s">
         <x:v>49</x:v>
@@ -4774,7 +4774,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>49</x:v>
@@ -4783,7 +4783,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
         <x:v>54</x:v>
@@ -4807,10 +4807,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>49</x:v>
@@ -4819,10 +4819,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB30" s="12" t="s">
         <x:v>49</x:v>
@@ -4831,30 +4831,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="BD30" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BE30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF30" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG30" s="12">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BH30" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BI30" s="12">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="BJ30" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:62">
       <x:c r="A31" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>47</x:v>
@@ -4863,10 +4863,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>49</x:v>
@@ -4875,10 +4875,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
         <x:v>49</x:v>
@@ -4887,10 +4887,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N31" s="12" t="s">
         <x:v>49</x:v>
@@ -4911,13 +4911,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="W31" s="12">
         <x:v>19</x:v>
@@ -4926,7 +4926,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
         <x:v>49</x:v>
@@ -4935,19 +4935,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AE31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
         <x:v>48</x:v>
@@ -4962,7 +4962,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4971,10 +4971,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
         <x:v>49</x:v>
@@ -4983,10 +4983,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>49</x:v>
@@ -4995,10 +4995,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX31" s="12" t="s">
         <x:v>49</x:v>
@@ -5007,10 +5007,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
         <x:v>49</x:v>
@@ -5019,30 +5019,30 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE31" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF31" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG31" s="12">
-        <x:v>47</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="BH31" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="BI31" s="12">
-        <x:v>62</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BJ31" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:62">
       <x:c r="A32" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>47</x:v>
@@ -5051,10 +5051,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
         <x:v>49</x:v>
@@ -5063,7 +5063,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
         <x:v>54</x:v>
@@ -5075,10 +5075,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M32" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N32" s="12" t="s">
         <x:v>49</x:v>
@@ -5099,22 +5099,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
         <x:v>49</x:v>
@@ -5123,7 +5123,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
         <x:v>51</x:v>
@@ -5135,10 +5135,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
         <x:v>49</x:v>
@@ -5147,10 +5147,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
         <x:v>49</x:v>
@@ -5159,10 +5159,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
         <x:v>49</x:v>
@@ -5171,7 +5171,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
         <x:v>54</x:v>
@@ -5183,7 +5183,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
         <x:v>54</x:v>
@@ -5195,10 +5195,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
         <x:v>49</x:v>
@@ -5210,27 +5210,27 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF32" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG32" s="12">
-        <x:v>57</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="BH32" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI32" s="12">
-        <x:v>62</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BJ32" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:62">
       <x:c r="A33" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>47</x:v>
@@ -5239,10 +5239,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F33" s="12" t="s">
         <x:v>49</x:v>
@@ -5251,10 +5251,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J33" s="12" t="s">
         <x:v>49</x:v>
@@ -5263,13 +5263,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M33" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N33" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O33" s="12">
         <x:v>21</x:v>
@@ -5287,13 +5287,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W33" s="12">
         <x:v>21</x:v>
@@ -5302,7 +5302,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
         <x:v>49</x:v>
@@ -5311,10 +5311,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD33" s="12" t="s">
         <x:v>49</x:v>
@@ -5323,10 +5323,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH33" s="12" t="s">
         <x:v>49</x:v>
@@ -5338,7 +5338,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AL33" s="12" t="s">
         <x:v>49</x:v>
@@ -5359,7 +5359,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
         <x:v>54</x:v>
@@ -5371,10 +5371,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>49</x:v>
@@ -5383,13 +5383,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB33" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC33" s="12">
         <x:v>21</x:v>
@@ -5398,19 +5398,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF33" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG33" s="12">
-        <x:v>6</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BH33" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI33" s="12">
-        <x:v>6</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ33" s="12" t="s">
         <x:v>115</x:v>
@@ -5427,10 +5427,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>49</x:v>
@@ -5451,10 +5451,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="L34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>49</x:v>
@@ -5478,19 +5478,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>49</x:v>
@@ -5499,7 +5499,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
         <x:v>51</x:v>
@@ -5511,10 +5511,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>49</x:v>
@@ -5523,10 +5523,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>49</x:v>
@@ -5535,10 +5535,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>49</x:v>
@@ -5547,7 +5547,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
         <x:v>54</x:v>
@@ -5559,7 +5559,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
         <x:v>54</x:v>
@@ -5571,7 +5571,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
         <x:v>54</x:v>
@@ -5586,22 +5586,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF34" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG34" s="12">
-        <x:v>42</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BH34" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI34" s="12">
-        <x:v>92</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ34" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:62">
@@ -5615,7 +5615,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
         <x:v>49</x:v>
@@ -5630,7 +5630,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>49</x:v>
@@ -5639,13 +5639,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="O35" s="12">
         <x:v>23</x:v>
@@ -5666,16 +5666,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
         <x:v>49</x:v>
@@ -5687,10 +5687,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>49</x:v>
@@ -5702,7 +5702,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>49</x:v>
@@ -5711,10 +5711,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
         <x:v>49</x:v>
@@ -5726,7 +5726,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>49</x:v>
@@ -5735,10 +5735,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
         <x:v>49</x:v>
@@ -5747,10 +5747,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
         <x:v>49</x:v>
@@ -5759,42 +5759,42 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AZ35" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA35" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BC35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="BD35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF35" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG35" s="12">
-        <x:v>42</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BH35" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BI35" s="12">
-        <x:v>72</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BJ35" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:62">
       <x:c r="A36" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>47</x:v>
@@ -5803,10 +5803,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>49</x:v>
@@ -5815,10 +5815,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
         <x:v>49</x:v>
@@ -5827,10 +5827,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N36" s="12" t="s">
         <x:v>49</x:v>
@@ -5851,22 +5851,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
         <x:v>49</x:v>
@@ -5875,22 +5875,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>49</x:v>
@@ -5899,10 +5899,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL36" s="12" t="s">
         <x:v>49</x:v>
@@ -5911,10 +5911,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>49</x:v>
@@ -5923,10 +5923,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>49</x:v>
@@ -5935,10 +5935,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>49</x:v>
@@ -5947,7 +5947,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AZ36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA36" s="12" t="s">
         <x:v>54</x:v>
@@ -5959,25 +5959,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="BD36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF36" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG36" s="12">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="BH36" s="12" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BI36" s="12">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="BJ36" s="12" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="BH36" s="12" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="BI36" s="12">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="BJ36" s="12" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:62">
@@ -5994,7 +5994,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -6003,10 +6003,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>49</x:v>
@@ -6015,10 +6015,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L37" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>49</x:v>
@@ -6039,22 +6039,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="W37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
         <x:v>49</x:v>
@@ -6063,7 +6063,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
         <x:v>51</x:v>
@@ -6078,7 +6078,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>49</x:v>
@@ -6090,7 +6090,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -6111,10 +6111,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
         <x:v>49</x:v>
@@ -6123,10 +6123,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
         <x:v>49</x:v>
@@ -6138,7 +6138,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
         <x:v>49</x:v>
@@ -6147,25 +6147,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE37" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG37" s="12">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH37" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BI37" s="12">
-        <x:v>62</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BJ37" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:62">
@@ -6173,16 +6173,16 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>49</x:v>
@@ -6191,10 +6191,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -6203,10 +6203,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N38" s="12" t="s">
         <x:v>49</x:v>
@@ -6227,10 +6227,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
         <x:v>49</x:v>
@@ -6239,10 +6239,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
         <x:v>49</x:v>
@@ -6251,22 +6251,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AD38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AE38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -6275,22 +6275,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AL38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AM38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
         <x:v>49</x:v>
@@ -6299,10 +6299,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>49</x:v>
@@ -6311,13 +6311,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY38" s="12">
         <x:v>26</x:v>
@@ -6326,7 +6326,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
         <x:v>49</x:v>
@@ -6335,30 +6335,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="BD38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE38" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF38" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG38" s="12">
-        <x:v>145</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BH38" s="12" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="BI38" s="12">
-        <x:v>298</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="BJ38" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:62">
       <x:c r="A39" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>47</x:v>
@@ -6367,7 +6367,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>51</x:v>
@@ -6379,10 +6379,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="H39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>49</x:v>
@@ -6391,10 +6391,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="L39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M39" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N39" s="12" t="s">
         <x:v>49</x:v>
@@ -6415,19 +6415,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
         <x:v>54</x:v>
@@ -6439,10 +6439,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6451,10 +6451,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6463,10 +6463,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6478,7 +6478,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP39" s="12" t="s">
         <x:v>49</x:v>
@@ -6487,10 +6487,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>49</x:v>
@@ -6499,10 +6499,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6511,10 +6511,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
@@ -6523,42 +6523,42 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BE39" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG39" s="12">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BH39" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI39" s="12">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BJ39" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62">
       <x:c r="A40" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>49</x:v>
@@ -6570,7 +6570,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>49</x:v>
@@ -6579,10 +6579,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N40" s="12" t="s">
         <x:v>49</x:v>
@@ -6606,7 +6606,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>49</x:v>
@@ -6618,7 +6618,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
         <x:v>49</x:v>
@@ -6627,10 +6627,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>49</x:v>
@@ -6642,7 +6642,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>49</x:v>
@@ -6666,7 +6666,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>49</x:v>
@@ -6690,19 +6690,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>49</x:v>
@@ -6711,22 +6711,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="BD40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE40" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG40" s="12">
-        <x:v>68</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="BH40" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="BI40" s="12">
-        <x:v>247</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="BJ40" s="12" t="s">
         <x:v>129</x:v>
@@ -6743,7 +6743,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
         <x:v>51</x:v>
@@ -6755,10 +6755,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>49</x:v>
@@ -6767,10 +6767,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N41" s="12" t="s">
         <x:v>49</x:v>
@@ -6791,19 +6791,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="W41" s="12">
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
         <x:v>54</x:v>
@@ -6815,10 +6815,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AB41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>49</x:v>
@@ -6827,10 +6827,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AF41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>49</x:v>
@@ -6854,7 +6854,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>49</x:v>
@@ -6866,7 +6866,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>49</x:v>
@@ -6875,7 +6875,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
         <x:v>50</x:v>
@@ -6887,10 +6887,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AZ41" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>49</x:v>
@@ -6899,42 +6899,42 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG41" s="12">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="BH41" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI41" s="12">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="BJ41" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62">
       <x:c r="A42" s="11" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F42" s="12" t="s">
         <x:v>49</x:v>
@@ -6943,10 +6943,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J42" s="12" t="s">
         <x:v>49</x:v>
@@ -6955,10 +6955,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N42" s="12" t="s">
         <x:v>49</x:v>
@@ -6979,10 +6979,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V42" s="12" t="s">
         <x:v>49</x:v>
@@ -6991,10 +6991,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
         <x:v>49</x:v>
@@ -7003,10 +7003,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD42" s="12" t="s">
         <x:v>49</x:v>
@@ -7015,10 +7015,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH42" s="12" t="s">
         <x:v>49</x:v>
@@ -7027,10 +7027,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL42" s="12" t="s">
         <x:v>49</x:v>
@@ -7039,10 +7039,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP42" s="12" t="s">
         <x:v>49</x:v>
@@ -7051,10 +7051,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>49</x:v>
@@ -7063,10 +7063,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
         <x:v>49</x:v>
@@ -7075,10 +7075,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BB42" s="12" t="s">
         <x:v>49</x:v>
@@ -7087,7 +7087,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE42" s="12" t="s">
         <x:v>50</x:v>
@@ -7096,16 +7096,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG42" s="12">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BH42" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI42" s="12">
-        <x:v>106</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="BJ42" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:62">
@@ -7113,16 +7113,16 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
         <x:v>49</x:v>
@@ -7131,10 +7131,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
         <x:v>49</x:v>
@@ -7143,10 +7143,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N43" s="12" t="s">
         <x:v>49</x:v>
@@ -7167,22 +7167,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
         <x:v>49</x:v>
@@ -7191,10 +7191,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>49</x:v>
@@ -7203,10 +7203,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>49</x:v>
@@ -7215,10 +7215,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>49</x:v>
@@ -7227,10 +7227,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
         <x:v>49</x:v>
@@ -7239,10 +7239,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
         <x:v>49</x:v>
@@ -7251,10 +7251,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
         <x:v>49</x:v>
@@ -7263,10 +7263,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
         <x:v>49</x:v>
@@ -7275,25 +7275,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="BD43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF43" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG43" s="12">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH43" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BI43" s="12">
-        <x:v>57</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BJ43" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:62">
@@ -7301,16 +7301,16 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
         <x:v>49</x:v>
@@ -7319,22 +7319,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="L44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N44" s="12" t="s">
         <x:v>49</x:v>
@@ -7355,22 +7355,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="W44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
         <x:v>49</x:v>
@@ -7379,10 +7379,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AB44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>49</x:v>
@@ -7391,10 +7391,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>49</x:v>
@@ -7403,10 +7403,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AJ44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
         <x:v>49</x:v>
@@ -7415,10 +7415,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AN44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>49</x:v>
@@ -7427,10 +7427,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
         <x:v>49</x:v>
@@ -7439,22 +7439,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY44" s="12">
         <x:v>32</x:v>
       </x:c>
       <x:c r="AZ44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
         <x:v>49</x:v>
@@ -7463,30 +7463,30 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG44" s="12">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BH44" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BI44" s="12">
-        <x:v>148</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BJ44" s="12" t="s">
-        <x:v>137</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:62">
       <x:c r="A45" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>47</x:v>
@@ -7507,10 +7507,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
         <x:v>49</x:v>
@@ -7519,10 +7519,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N45" s="12" t="s">
         <x:v>49</x:v>
@@ -7543,22 +7543,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
         <x:v>49</x:v>
@@ -7567,10 +7567,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
         <x:v>49</x:v>
@@ -7579,7 +7579,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
         <x:v>51</x:v>
@@ -7591,10 +7591,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
         <x:v>49</x:v>
@@ -7603,7 +7603,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
         <x:v>54</x:v>
@@ -7615,10 +7615,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
         <x:v>49</x:v>
@@ -7627,10 +7627,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
         <x:v>49</x:v>
@@ -7639,10 +7639,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
         <x:v>49</x:v>
@@ -7654,27 +7654,27 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="BE45" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG45" s="12">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BH45" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BI45" s="12">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BJ45" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:62">
       <x:c r="A46" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>47</x:v>
@@ -7686,7 +7686,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>49</x:v>
@@ -7695,10 +7695,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>49</x:v>
@@ -7707,10 +7707,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L46" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M46" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N46" s="12" t="s">
         <x:v>49</x:v>
@@ -7731,22 +7731,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
         <x:v>49</x:v>
@@ -7755,10 +7755,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>49</x:v>
@@ -7767,10 +7767,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>49</x:v>
@@ -7779,10 +7779,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>49</x:v>
@@ -7791,10 +7791,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
         <x:v>49</x:v>
@@ -7806,7 +7806,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
         <x:v>49</x:v>
@@ -7815,10 +7815,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
         <x:v>49</x:v>
@@ -7827,10 +7827,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
         <x:v>49</x:v>
@@ -7848,21 +7848,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG46" s="12">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BH46" s="12" t="s">
-        <x:v>131</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BI46" s="12">
-        <x:v>139</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="BJ46" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:62">
       <x:c r="A47" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
         <x:v>47</x:v>
@@ -7874,7 +7874,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7883,7 +7883,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
         <x:v>54</x:v>
@@ -7895,10 +7895,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N47" s="12" t="s">
         <x:v>49</x:v>
@@ -7919,22 +7919,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="W47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
         <x:v>49</x:v>
@@ -7943,10 +7943,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7958,7 +7958,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7982,7 +7982,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
         <x:v>49</x:v>
@@ -7994,7 +7994,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
         <x:v>49</x:v>
@@ -8003,7 +8003,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
         <x:v>54</x:v>
@@ -8015,10 +8015,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
@@ -8030,39 +8030,39 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="BE47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG47" s="12">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BH47" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="BI47" s="12">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BJ47" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:62">
       <x:c r="A48" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>49</x:v>
@@ -8071,10 +8071,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>49</x:v>
@@ -8083,10 +8083,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N48" s="12" t="s">
         <x:v>49</x:v>
@@ -8107,22 +8107,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="W48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
         <x:v>49</x:v>
@@ -8131,10 +8131,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>49</x:v>
@@ -8143,10 +8143,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -8155,10 +8155,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -8167,10 +8167,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
         <x:v>49</x:v>
@@ -8179,10 +8179,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
         <x:v>49</x:v>
@@ -8191,22 +8191,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB48" s="12" t="s">
         <x:v>49</x:v>
@@ -8215,42 +8215,42 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="BD48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE48" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG48" s="12">
-        <x:v>142</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BH48" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BI48" s="12">
-        <x:v>285</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BJ48" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:62">
       <x:c r="A49" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>49</x:v>
@@ -8259,10 +8259,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J49" s="12" t="s">
         <x:v>49</x:v>
@@ -8271,10 +8271,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N49" s="12" t="s">
         <x:v>49</x:v>
@@ -8295,10 +8295,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V49" s="12" t="s">
         <x:v>49</x:v>
@@ -8307,10 +8307,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
         <x:v>49</x:v>
@@ -8319,10 +8319,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>49</x:v>
@@ -8331,10 +8331,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF49" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>49</x:v>
@@ -8343,10 +8343,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -8355,10 +8355,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
         <x:v>49</x:v>
@@ -8367,10 +8367,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
         <x:v>49</x:v>
@@ -8379,10 +8379,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>49</x:v>
@@ -8391,10 +8391,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AZ49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
         <x:v>49</x:v>
@@ -8403,30 +8403,30 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE49" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF49" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG49" s="12">
-        <x:v>67</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BH49" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="BI49" s="12">
-        <x:v>113</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="BJ49" s="12" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:62">
       <x:c r="A50" s="11" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
         <x:v>47</x:v>
@@ -8435,10 +8435,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>49</x:v>
@@ -8450,7 +8450,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>49</x:v>
@@ -8459,10 +8459,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M50" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N50" s="12" t="s">
         <x:v>49</x:v>
@@ -8483,22 +8483,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V50" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="W50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>49</x:v>
@@ -8507,7 +8507,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>51</x:v>
@@ -8519,7 +8519,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
         <x:v>51</x:v>
@@ -8534,7 +8534,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AL50" s="12" t="s">
         <x:v>49</x:v>
@@ -8543,10 +8543,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
         <x:v>49</x:v>
@@ -8558,7 +8558,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>49</x:v>
@@ -8567,10 +8567,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>49</x:v>
@@ -8579,10 +8579,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
         <x:v>49</x:v>
@@ -8591,42 +8591,42 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="BD50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE50" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF50" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG50" s="12">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="BH50" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="BI50" s="12">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="BJ50" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:62">
       <x:c r="A51" s="11" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>49</x:v>
@@ -8635,10 +8635,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>49</x:v>
@@ -8647,10 +8647,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N51" s="12" t="s">
         <x:v>49</x:v>
@@ -8671,22 +8671,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="W51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
         <x:v>49</x:v>
@@ -8695,10 +8695,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>49</x:v>
@@ -8707,10 +8707,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>49</x:v>
@@ -8719,10 +8719,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>49</x:v>
@@ -8731,10 +8731,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP51" s="12" t="s">
         <x:v>49</x:v>
@@ -8743,7 +8743,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
         <x:v>49</x:v>
@@ -8755,22 +8755,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AV51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="BB51" s="12" t="s">
         <x:v>49</x:v>
@@ -8779,7 +8779,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE51" s="12" t="s">
         <x:v>50</x:v>
@@ -8788,30 +8788,30 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG51" s="12">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="BH51" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="BI51" s="12">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="BJ51" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:62">
       <x:c r="A52" s="11" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>136</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
         <x:v>49</x:v>
@@ -8823,10 +8823,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>49</x:v>
@@ -8835,10 +8835,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N52" s="12" t="s">
         <x:v>49</x:v>
@@ -8859,22 +8859,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="W52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
         <x:v>49</x:v>
@@ -8883,10 +8883,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AB52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>49</x:v>
@@ -8895,10 +8895,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>49</x:v>
@@ -8907,10 +8907,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>49</x:v>
@@ -8919,10 +8919,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
         <x:v>49</x:v>
@@ -8931,10 +8931,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
         <x:v>49</x:v>
@@ -8943,22 +8943,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
         <x:v>49</x:v>
@@ -8967,42 +8967,42 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="BD52" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG52" s="12">
-        <x:v>0</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BH52" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI52" s="12">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="BJ52" s="12" t="s">
-        <x:v>115</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:62">
       <x:c r="A53" s="11" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>49</x:v>
@@ -9011,10 +9011,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>49</x:v>
@@ -9023,7 +9023,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M53" s="12" t="s">
         <x:v>55</x:v>
@@ -9047,22 +9047,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
         <x:v>49</x:v>
@@ -9071,10 +9071,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>49</x:v>
@@ -9083,10 +9083,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -9095,10 +9095,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>49</x:v>
@@ -9107,10 +9107,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AN53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
         <x:v>49</x:v>
@@ -9119,10 +9119,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
         <x:v>49</x:v>
@@ -9131,10 +9131,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>49</x:v>
@@ -9143,10 +9143,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
         <x:v>49</x:v>
@@ -9155,25 +9155,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BE53" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF53" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG53" s="12">
-        <x:v>118</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="BH53" s="12" t="s">
         <x:v>149</x:v>
       </x:c>
       <x:c r="BI53" s="12">
-        <x:v>144</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="BJ53" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:62">
@@ -9187,10 +9187,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>49</x:v>
@@ -9199,10 +9199,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
         <x:v>49</x:v>
@@ -9211,10 +9211,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="M54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N54" s="12" t="s">
         <x:v>49</x:v>
@@ -9235,10 +9235,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>49</x:v>
@@ -9250,19 +9250,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -9274,7 +9274,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>49</x:v>
@@ -9283,10 +9283,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -9295,10 +9295,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
         <x:v>49</x:v>
@@ -9307,10 +9307,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
         <x:v>49</x:v>
@@ -9319,7 +9319,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
         <x:v>54</x:v>
@@ -9331,10 +9331,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BB54" s="12" t="s">
         <x:v>49</x:v>
@@ -9343,25 +9343,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG54" s="12">
-        <x:v>34</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BH54" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BI54" s="12">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BJ54" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:62">
@@ -9375,10 +9375,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>49</x:v>
@@ -9387,10 +9387,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J55" s="12" t="s">
         <x:v>49</x:v>
@@ -9399,13 +9399,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M55" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N55" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O55" s="12">
         <x:v>43</x:v>
@@ -9423,19 +9423,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
         <x:v>51</x:v>
@@ -9447,10 +9447,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD55" s="12" t="s">
         <x:v>49</x:v>
@@ -9459,7 +9459,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
         <x:v>50</x:v>
@@ -9471,10 +9471,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AL55" s="12" t="s">
         <x:v>49</x:v>
@@ -9483,10 +9483,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
         <x:v>49</x:v>
@@ -9495,10 +9495,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
         <x:v>49</x:v>
@@ -9507,10 +9507,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX55" s="12" t="s">
         <x:v>49</x:v>
@@ -9519,10 +9519,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AZ55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
         <x:v>49</x:v>
@@ -9531,25 +9531,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BE55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG55" s="12">
-        <x:v>35</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="BH55" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="BI55" s="12">
-        <x:v>37</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="BJ55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:62">
@@ -9563,10 +9563,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>49</x:v>
@@ -9575,10 +9575,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>49</x:v>
@@ -9587,10 +9587,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="L56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N56" s="12" t="s">
         <x:v>49</x:v>
@@ -9611,22 +9611,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="V56" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="W56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="X56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9635,10 +9635,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>49</x:v>
@@ -9647,10 +9647,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>49</x:v>
@@ -9659,10 +9659,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9671,10 +9671,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
         <x:v>49</x:v>
@@ -9683,10 +9683,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
         <x:v>49</x:v>
@@ -9695,10 +9695,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
         <x:v>49</x:v>
@@ -9707,10 +9707,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AZ56" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
         <x:v>49</x:v>
@@ -9719,25 +9719,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BE56" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BF56" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG56" s="12">
-        <x:v>89</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="BH56" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="BI56" s="12">
-        <x:v>95</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ56" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:62">
@@ -9745,16 +9745,16 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F57" s="12" t="s">
         <x:v>49</x:v>
@@ -9763,7 +9763,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
         <x:v>54</x:v>
@@ -9775,10 +9775,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N57" s="12" t="s">
         <x:v>49</x:v>
@@ -9799,22 +9799,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
         <x:v>49</x:v>
@@ -9823,10 +9823,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>49</x:v>
@@ -9835,10 +9835,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>49</x:v>
@@ -9847,10 +9847,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9859,10 +9859,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
         <x:v>49</x:v>
@@ -9871,10 +9871,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AR57" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
         <x:v>49</x:v>
@@ -9883,10 +9883,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>49</x:v>
@@ -9895,10 +9895,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BB57" s="12" t="s">
         <x:v>49</x:v>
@@ -9907,7 +9907,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="BD57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE57" s="12" t="s">
         <x:v>50</x:v>
@@ -9916,16 +9916,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG57" s="12">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BH57" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BI57" s="12">
-        <x:v>41</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="BJ57" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:62">
@@ -9939,10 +9939,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
         <x:v>49</x:v>
@@ -9951,10 +9951,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
         <x:v>49</x:v>
@@ -9963,10 +9963,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="L58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M58" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N58" s="12" t="s">
         <x:v>49</x:v>
@@ -9987,10 +9987,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>49</x:v>
@@ -9999,10 +9999,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
         <x:v>49</x:v>
@@ -10011,10 +10011,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="s">
         <x:v>49</x:v>
@@ -10023,10 +10023,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH58" s="12" t="s">
         <x:v>49</x:v>
@@ -10035,10 +10035,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AJ58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK58" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AL58" s="12" t="s">
         <x:v>49</x:v>
@@ -10047,10 +10047,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
         <x:v>49</x:v>
@@ -10059,10 +10059,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
         <x:v>49</x:v>
@@ -10071,10 +10071,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX58" s="12" t="s">
         <x:v>49</x:v>
@@ -10083,10 +10083,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
         <x:v>49</x:v>
@@ -10095,42 +10095,42 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE58" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BF58" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG58" s="12">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BH58" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BI58" s="12">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="BJ58" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:62">
       <x:c r="A59" s="11" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
         <x:v>49</x:v>
@@ -10139,10 +10139,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H59" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J59" s="12" t="s">
         <x:v>49</x:v>
@@ -10151,10 +10151,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="L59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N59" s="12" t="s">
         <x:v>49</x:v>
@@ -10175,10 +10175,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V59" s="12" t="s">
         <x:v>49</x:v>
@@ -10187,10 +10187,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="X59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>49</x:v>
@@ -10199,10 +10199,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>49</x:v>
@@ -10211,10 +10211,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>49</x:v>
@@ -10223,10 +10223,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
         <x:v>49</x:v>
@@ -10235,10 +10235,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
         <x:v>49</x:v>
@@ -10247,10 +10247,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>49</x:v>
@@ -10259,10 +10259,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>49</x:v>
@@ -10271,10 +10271,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB59" s="12" t="s">
         <x:v>49</x:v>
@@ -10283,30 +10283,30 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="BD59" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BE59" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF59" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG59" s="12">
-        <x:v>79</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BH59" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BI59" s="12">
-        <x:v>79</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BJ59" s="12" t="s">
-        <x:v>155</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:62">
       <x:c r="A60" s="11" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>47</x:v>
@@ -10315,10 +10315,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F60" s="12" t="s">
         <x:v>49</x:v>
@@ -10327,169 +10327,169 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M60" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="O60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P60" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="Q60" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="R60" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="S60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="T60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="U60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="V60" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="W60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="X60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="Y60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Z60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AA60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AB60" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AC60" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AD60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AE60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AF60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AG60" s="12" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="AH60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AI60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AJ60" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AK60" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="AL60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AM60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AN60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AO60" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AP60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AQ60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AR60" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AS60" s="12" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AT60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AU60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AV60" s="12" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AW60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AX60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AY60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="AZ60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BA60" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BB60" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BC60" s="12">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="BD60" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BE60" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L60" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="M60" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="N60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="P60" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="Q60" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="R60" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="S60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="T60" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="U60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="V60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="W60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="X60" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="Y60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="Z60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AA60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AB60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AC60" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AD60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AE60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AF60" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AG60" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="AH60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AI60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AJ60" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="AK60" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AL60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AM60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AN60" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AO60" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AP60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AQ60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AR60" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="AS60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AT60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AU60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AV60" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AW60" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="AX60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="AY60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AZ60" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="BA60" s="12" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="BB60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="BC60" s="12">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="BD60" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="BE60" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="BF60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BG60" s="12">
-        <x:v>17</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="BH60" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="BI60" s="12">
-        <x:v>17</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="BJ60" s="12" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:62">
@@ -10503,7 +10503,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
         <x:v>49</x:v>
@@ -10515,10 +10515,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
         <x:v>49</x:v>
@@ -10527,13 +10527,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="L61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="O61" s="12">
         <x:v>49</x:v>
@@ -10551,22 +10551,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="T61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="W61" s="12">
         <x:v>49</x:v>
       </x:c>
       <x:c r="X61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Y61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z61" s="12" t="s">
         <x:v>49</x:v>
@@ -10575,10 +10575,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AB61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD61" s="12" t="s">
         <x:v>49</x:v>
@@ -10587,10 +10587,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH61" s="12" t="s">
         <x:v>49</x:v>
@@ -10599,10 +10599,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AJ61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
         <x:v>49</x:v>
@@ -10611,10 +10611,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP61" s="12" t="s">
         <x:v>49</x:v>
@@ -10623,10 +10623,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AR61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>49</x:v>
@@ -10635,7 +10635,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
         <x:v>49</x:v>
@@ -10647,7 +10647,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
         <x:v>49</x:v>
@@ -10659,25 +10659,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BE61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BG61" s="12">
-        <x:v>6</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="BH61" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI61" s="12">
-        <x:v>6</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BJ61" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:62">
@@ -10691,7 +10691,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
         <x:v>49</x:v>
@@ -10703,10 +10703,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
         <x:v>49</x:v>
@@ -10715,10 +10715,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N62" s="12" t="s">
         <x:v>49</x:v>
@@ -10739,10 +10739,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
         <x:v>49</x:v>
@@ -10751,10 +10751,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
         <x:v>49</x:v>
@@ -10763,22 +10763,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
         <x:v>49</x:v>
@@ -10787,10 +10787,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL62" s="12" t="s">
         <x:v>49</x:v>
@@ -10799,10 +10799,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
         <x:v>49</x:v>
@@ -10811,10 +10811,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
         <x:v>49</x:v>
@@ -10823,10 +10823,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
         <x:v>49</x:v>
@@ -10835,37 +10835,37 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BG62" s="12">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="BH62" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BI62" s="12">
-        <x:v>0</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BJ62" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:62">
